--- a/data/LCIs/Lai_2025/Ni_LCIs_BW_Final_v1.xlsx
+++ b/data/LCIs/Lai_2025/Ni_LCIs_BW_Final_v1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="453" documentId="8_{D90A6F2A-0357-4B55-86BC-6D3D4F34DC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC0E887C-7F30-44BC-BB61-D46381B0D17A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="898" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="898" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -16119,6 +16119,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27027,6 +27028,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004741122952C13D46BBBC92EEAE11CF32" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d96b5fa62e5213e7d24e66b2bac0c378">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d78c010b-218d-4be4-b2d9-423b1f51aae5" xmlns:ns3="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2e8fc9a9c70fab2c0f7259df75af726" ns2:_="" ns3:_="">
     <xsd:import namespace="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
@@ -27249,17 +27261,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -27270,6 +27271,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F92CF09-C25F-448C-821E-AD94453B3152}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADCE0B9-F822-43B9-8FA4-0E5A537799BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27288,17 +27300,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F92CF09-C25F-448C-821E-AD94453B3152}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AB90B26-BD59-4509-808B-5C4F1D827BEA}">
   <ds:schemaRefs>
